--- a/outputs/TAS_curtailment.xlsx
+++ b/outputs/TAS_curtailment.xlsx
@@ -638,10 +638,10 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0069</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
@@ -700,7 +700,7 @@
         <v>0.0033</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
@@ -756,10 +756,10 @@
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.0136</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0193</v>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         <v>1.0088</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0069</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
         <v>0.0033</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
         <v>0.9188</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.0136</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0193</v>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>

--- a/outputs/TAS_curtailment.xlsx
+++ b/outputs/TAS_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -465,10 +465,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -482,6 +482,8 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,85 +519,95 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>REZ Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual FY24-25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Actual FY25-26</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ELI Source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -618,47 +630,41 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
         <v>0.0069</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="n">
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="5" t="n">
         <v>0.9923999999999999</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>1.0088</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
+      <c r="Y2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -677,47 +683,41 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="5" t="n">
         <v>0.0033</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="5" t="n">
         <v>0.9555</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="Q3" s="5" t="n">
         <v>0.9688</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -736,47 +736,41 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
         <v>0.0136</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4" s="5" t="n">
         <v>0.0193</v>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="5" t="n">
         <v>0.9101</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>0.9188</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
+      <c r="Y4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -795,43 +789,37 @@
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="5" t="n">
         <v>0.9224</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>0.9371</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
       <c r="W5" s="6" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1009,42 +997,18 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N2" s="5" t="inlineStr"/>
       <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1073,42 +1037,18 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1137,42 +1077,18 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1197,42 +1113,18 @@
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/outputs/TAS_curtailment.xlsx
+++ b/outputs/TAS_curtailment.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ELI Near Term</t>
+          <t>ELI Near Term (2026-28)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ELI Med Term</t>
+          <t>ELI Med Term (2030-35)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -630,9 +630,21 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Central Highlands</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
@@ -643,7 +655,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0014</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
@@ -657,14 +669,30 @@
       <c r="Q2" s="5" t="n">
         <v>1.0088</v>
       </c>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
-      <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
-      <c r="Y2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y2" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -683,9 +711,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>North West Tasmania</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
@@ -696,7 +736,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0012</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -710,14 +750,30 @@
       <c r="Q3" s="5" t="n">
         <v>0.9688</v>
       </c>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
-      <c r="Y3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X3" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y3" s="6" t="n">
+        <v>0.01333333333333333</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -736,9 +792,21 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>TAS</t>
@@ -989,27 +1057,67 @@
         <v>1.0088</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0014</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1029,27 +1137,67 @@
         <v>0.9688</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0012</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0.01333333333333333</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">

--- a/outputs/TAS_curtailment.xlsx
+++ b/outputs/TAS_curtailment.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,14 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,6 +618,46 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ match</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2029-30</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2039-40</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2049-50</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2029-30</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2039-40</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2049-50</t>
         </is>
       </c>
     </row>
@@ -693,6 +741,34 @@
       <c r="Y2" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Central Highlands</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB2" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC2" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AD2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -773,6 +849,34 @@
       </c>
       <c r="Y3" s="6" t="n">
         <v>0.01333333333333333</v>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>North West Tasmania</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB3" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -839,6 +943,14 @@
       <c r="W4" s="6" t="inlineStr"/>
       <c r="X4" s="6" t="inlineStr"/>
       <c r="Y4" s="6" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr"/>
+      <c r="AF4" s="6" t="inlineStr"/>
+      <c r="AG4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -888,6 +1000,14 @@
       <c r="W5" s="6" t="inlineStr"/>
       <c r="X5" s="6" t="inlineStr"/>
       <c r="Y5" s="6" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="6" t="inlineStr"/>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr"/>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -900,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -925,6 +1045,12 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1038,6 +1164,36 @@
           <t>ISP_OFFLOADING_AVG</t>
         </is>
       </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y1</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y2</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y3</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y1</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y2</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -1118,6 +1274,24 @@
       <c r="V2" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1197,6 +1371,24 @@
       </c>
       <c r="V3" s="5" t="n">
         <v>0.01333333333333333</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -1238,6 +1430,12 @@
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1274,6 +1472,12 @@
       <c r="T5" s="5" t="inlineStr"/>
       <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+      <c r="AB5" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C5">
@@ -1516,6 +1720,78 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W5">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X5">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y5">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z5">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA5">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB5">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>